--- a/PLANTILLA.xlsx
+++ b/PLANTILLA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\CMVA-SOFTWARE\CMVA IMAGENES DIAGNOSTICAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SISTEMAS\Documents\EQG\CMVA-XD\cmva_img_dx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07675B97-AE79-4948-91C0-CEF6BC837385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332F37C3-B8F9-4461-8C3A-F80AE0AF61D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{68686030-E28C-41F8-A464-A2CB9D28C07A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{68686030-E28C-41F8-A464-A2CB9D28C07A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>ID_REGISTRO</t>
   </si>
@@ -109,87 +106,6 @@
   </si>
   <si>
     <t>PROFESIONAL</t>
-  </si>
-  <si>
-    <t>1081275310</t>
-  </si>
-  <si>
-    <t>DANIEL CUELLAR</t>
-  </si>
-  <si>
-    <t>RX TORAX</t>
-  </si>
-  <si>
-    <t>URGENCIAS</t>
-  </si>
-  <si>
-    <t>HANYI</t>
-  </si>
-  <si>
-    <t>CAROLINA</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>BOLAÑOS</t>
-  </si>
-  <si>
-    <t>BONNY</t>
-  </si>
-  <si>
-    <t>LEIDO</t>
-  </si>
-  <si>
-    <t>Rayos X</t>
-  </si>
-  <si>
-    <t>Estado ok</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>DRA. MAGALY MORA</t>
-  </si>
-  <si>
-    <t>RX-2026-06-000001</t>
-  </si>
-  <si>
-    <t>RX-2026-06-000002</t>
-  </si>
-  <si>
-    <t>LUISA MONGE</t>
-  </si>
-  <si>
-    <t>TAC</t>
-  </si>
-  <si>
-    <t>TAC-2026-06-000002</t>
-  </si>
-  <si>
-    <t>MARTHA TORRES</t>
-  </si>
-  <si>
-    <t>HOSPITALIZACION</t>
-  </si>
-  <si>
-    <t>DR. CHAMORRO</t>
-  </si>
-  <si>
-    <t>PENDIENTE</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>TAC CADERA CONTRASTE</t>
-  </si>
-  <si>
-    <t>ML-000001</t>
   </si>
   <si>
     <t xml:space="preserve">VOLUMEN_CONTRASTE_ML </t>
@@ -199,7 +115,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,38 +123,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A3C5E"/>
-        <bgColor rgb="FF1A3C5E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -253,15 +144,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -280,9 +164,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -320,7 +204,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -426,7 +310,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -568,7 +452,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -576,294 +460,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F760DE3B-37AA-4326-8E2B-337B2A3C6D0A}">
-  <dimension ref="A1:Y4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Y1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="O1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>13</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>14</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="4">
-        <v>46174.088888888888</v>
-      </c>
-      <c r="D2" s="4">
-        <v>46174.088206018518</v>
-      </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="P2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="U2" s="5">
-        <v>46174.344444444447</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="4">
-        <v>46174.088946759257</v>
-      </c>
-      <c r="D3" s="4">
-        <v>46174.088414351849</v>
-      </c>
-      <c r="E3">
-        <v>66835726</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="P3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="U3" s="5">
-        <v>46174.344444444447</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="4">
-        <v>46174.088946759257</v>
-      </c>
-      <c r="D4" s="4">
-        <v>46174.088414351849</v>
-      </c>
-      <c r="E4">
-        <v>66835758</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>3</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>3</v>
-      </c>
-      <c r="P4" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
